--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>91751</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,23 +1089,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1113,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R6" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1145,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>91751</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1182,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R7" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,6 +1242,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533500</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130533501</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130533502</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>130533503</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B6" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,19 +1089,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1109,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R6" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R7" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1242,11 +1247,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130533508</v>
       </c>
       <c r="B7" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533500</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130533501</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130533502</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,23 +1089,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1113,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R6" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1145,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>91779</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1182,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R7" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,6 +1242,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>130533503</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,19 +1089,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1109,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R6" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R7" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1242,11 +1247,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,23 +1089,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1113,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R6" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1145,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1182,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R7" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,6 +1242,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533500</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130533501</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130533502</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>130533503</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533500</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130533501</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130533502</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>130533503</v>
       </c>
       <c r="B9" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130533500</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130533493</v>
       </c>
       <c r="B3" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>130533501</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130533502</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>130533507</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>130533503</v>
       </c>
       <c r="B9" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B6" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,19 +1089,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1109,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R6" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R7" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1242,11 +1247,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533494</v>
+        <v>130533508</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,23 +1089,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1113,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454680</v>
+        <v>454771</v>
       </c>
       <c r="R6" t="n">
-        <v>6957331</v>
+        <v>6957552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1145,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533508</v>
+        <v>130533494</v>
       </c>
       <c r="B7" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,19 +1182,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1211,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454771</v>
+        <v>454680</v>
       </c>
       <c r="R7" t="n">
-        <v>6957552</v>
+        <v>6957331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1247,6 +1242,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130533500</v>
+        <v>130533493</v>
       </c>
       <c r="B2" t="n">
-        <v>57878</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454726</v>
+        <v>454645</v>
       </c>
       <c r="R2" t="n">
-        <v>6957560</v>
+        <v>6957513</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +772,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130533493</v>
+        <v>130533503</v>
       </c>
       <c r="B3" t="n">
-        <v>91802</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Havsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454645</v>
+        <v>454784</v>
       </c>
       <c r="R3" t="n">
-        <v>6957513</v>
+        <v>6957149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130533501</v>
+        <v>130533494</v>
       </c>
       <c r="B4" t="n">
-        <v>57878</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454765</v>
+        <v>454680</v>
       </c>
       <c r="R4" t="n">
-        <v>6957387</v>
+        <v>6957331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +956,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130533502</v>
+        <v>130533500</v>
       </c>
       <c r="B5" t="n">
-        <v>57878</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454798</v>
+        <v>454726</v>
       </c>
       <c r="R5" t="n">
-        <v>6957350</v>
+        <v>6957560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1058,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130533508</v>
+        <v>130533501</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,19 +1096,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1109,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454771</v>
+        <v>454765</v>
       </c>
       <c r="R6" t="n">
-        <v>6957552</v>
+        <v>6957387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,6 +1156,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1171,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130533494</v>
+        <v>130533502</v>
       </c>
       <c r="B7" t="n">
-        <v>57878</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454680</v>
+        <v>454798</v>
       </c>
       <c r="R7" t="n">
-        <v>6957331</v>
+        <v>6957350</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,208 +1286,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130533507</v>
-      </c>
-      <c r="B8" t="n">
-        <v>91822</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Havsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>454701</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6957548</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>130533503</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57875</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Havsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>454784</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6957149</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58238-2025 artfynd.xlsx
+++ b/artfynd/A 58238-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533494</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533500</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533501</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,8 +1316,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130533502</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>